--- a/astro-site/public/dl/guia-restaurante-mexicano/menu-engineering-matrix.xlsx
+++ b/astro-site/public/dl/guia-restaurante-mexicano/menu-engineering-matrix.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Matrix'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -508,9 +510,9 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -530,6 +532,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -558,10 +561,19 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/guia-restaurante-mexicano · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -570,7 +582,16 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -579,7 +600,7 @@
   <sheetPr>
     <tabColor rgb="009C27B0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -610,6 +631,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -679,18 +701,18 @@
       </c>
       <c r="E5" s="10">
         <f>D5/C5</f>
-        <v/>
+        <v>0.26666666666666666</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>150</v>
       </c>
       <c r="G5" s="11">
         <f>C5-D5</f>
-        <v/>
+        <v>3.3</v>
       </c>
       <c r="H5" s="11">
         <f>G5*F5</f>
-        <v/>
+        <v>495.0</v>
       </c>
     </row>
     <row r="6">
@@ -710,18 +732,18 @@
       </c>
       <c r="E6" s="10">
         <f>D6/C6</f>
-        <v/>
+        <v>0.225</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>120</v>
       </c>
       <c r="G6" s="11">
         <f>C6-D6</f>
-        <v/>
+        <v>6.2</v>
       </c>
       <c r="H6" s="11">
         <f>G6*F6</f>
-        <v/>
+        <v>744.0</v>
       </c>
     </row>
     <row r="7">
@@ -741,18 +763,18 @@
       </c>
       <c r="E7" s="10">
         <f>D7/C7</f>
-        <v/>
+        <v>0.1523809523809524</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>70</v>
       </c>
       <c r="G7" s="11">
         <f>C7-D7</f>
-        <v/>
+        <v>8.9</v>
       </c>
       <c r="H7" s="11">
         <f>G7*F7</f>
-        <v/>
+        <v>623.0</v>
       </c>
     </row>
     <row r="8">
@@ -772,18 +794,18 @@
       </c>
       <c r="E8" s="10">
         <f>D8/C8</f>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>90</v>
       </c>
       <c r="G8" s="11">
         <f>C8-D8</f>
-        <v/>
+        <v>8.8</v>
       </c>
       <c r="H8" s="11">
         <f>G8*F8</f>
-        <v/>
+        <v>792.0000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -803,18 +825,18 @@
       </c>
       <c r="E9" s="10">
         <f>D9/C9</f>
-        <v/>
+        <v>0.16666666666666666</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>100</v>
       </c>
       <c r="G9" s="11">
         <f>C9-D9</f>
-        <v/>
+        <v>7.5</v>
       </c>
       <c r="H9" s="11">
         <f>G9*F9</f>
-        <v/>
+        <v>750.0</v>
       </c>
     </row>
     <row r="10">
@@ -834,18 +856,18 @@
       </c>
       <c r="E10" s="10">
         <f>D10/C10</f>
-        <v/>
+        <v>0.14285714285714285</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>55</v>
       </c>
       <c r="G10" s="11">
         <f>C10-D10</f>
-        <v/>
+        <v>6.0</v>
       </c>
       <c r="H10" s="11">
         <f>G10*F10</f>
-        <v/>
+        <v>330.0</v>
       </c>
     </row>
     <row r="11">
@@ -865,18 +887,18 @@
       </c>
       <c r="E11" s="10">
         <f>D11/C11</f>
-        <v/>
+        <v>0.19230769230769232</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>40</v>
       </c>
       <c r="G11" s="11">
         <f>C11-D11</f>
-        <v/>
+        <v>10.5</v>
       </c>
       <c r="H11" s="11">
         <f>G11*F11</f>
-        <v/>
+        <v>420.0</v>
       </c>
     </row>
     <row r="12">
@@ -896,18 +918,18 @@
       </c>
       <c r="E12" s="10">
         <f>D12/C12</f>
-        <v/>
+        <v>0.25925925925925924</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>35</v>
       </c>
       <c r="G12" s="11">
         <f>C12-D12</f>
-        <v/>
+        <v>10.0</v>
       </c>
       <c r="H12" s="11">
         <f>G12*F12</f>
-        <v/>
+        <v>350.0</v>
       </c>
     </row>
     <row r="13">
@@ -927,18 +949,18 @@
       </c>
       <c r="E13" s="10">
         <f>D13/C13</f>
-        <v/>
+        <v>0.16666666666666666</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>200</v>
       </c>
       <c r="G13" s="11">
         <f>C13-D13</f>
-        <v/>
+        <v>7.5</v>
       </c>
       <c r="H13" s="11">
         <f>G13*F13</f>
-        <v/>
+        <v>1500.0</v>
       </c>
     </row>
     <row r="14">
@@ -958,18 +980,18 @@
       </c>
       <c r="E14" s="10">
         <f>D14/C14</f>
-        <v/>
+        <v>0.12307692307692308</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>85</v>
       </c>
       <c r="G14" s="11">
         <f>C14-D14</f>
-        <v/>
+        <v>5.7</v>
       </c>
       <c r="H14" s="11">
         <f>G14*F14</f>
-        <v/>
+        <v>484.5</v>
       </c>
     </row>
     <row r="15">
@@ -989,18 +1011,18 @@
       </c>
       <c r="E15" s="10">
         <f>D15/C15</f>
-        <v/>
+        <v>0.18181818181818182</v>
       </c>
       <c r="F15" s="8" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="11">
         <f>C15-D15</f>
-        <v/>
+        <v>9.0</v>
       </c>
       <c r="H15" s="11">
         <f>G15*F15</f>
-        <v/>
+        <v>270.0</v>
       </c>
     </row>
     <row r="16">
@@ -1020,18 +1042,18 @@
       </c>
       <c r="E16" s="10">
         <f>D16/C16</f>
-        <v/>
+        <v>0.16363636363636364</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>25</v>
       </c>
       <c r="G16" s="11">
         <f>C16-D16</f>
-        <v/>
+        <v>9.2</v>
       </c>
       <c r="H16" s="11">
         <f>G16*F16</f>
-        <v/>
+        <v>229.99999999999997</v>
       </c>
     </row>
     <row r="17">
@@ -1051,18 +1073,18 @@
       </c>
       <c r="E17" s="10">
         <f>D17/C17</f>
-        <v/>
+        <v>0.10909090909090909</v>
       </c>
       <c r="F17" s="8" t="n">
         <v>65</v>
       </c>
       <c r="G17" s="11">
         <f>C17-D17</f>
-        <v/>
+        <v>4.9</v>
       </c>
       <c r="H17" s="11">
         <f>G17*F17</f>
-        <v/>
+        <v>318.5</v>
       </c>
     </row>
     <row r="18">
@@ -1082,18 +1104,18 @@
       </c>
       <c r="E18" s="10">
         <f>D18/C18</f>
-        <v/>
+        <v>0.3111111111111111</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>110</v>
       </c>
       <c r="G18" s="11">
         <f>C18-D18</f>
-        <v/>
+        <v>3.1</v>
       </c>
       <c r="H18" s="11">
         <f>G18*F18</f>
-        <v/>
+        <v>341.0</v>
       </c>
     </row>
     <row r="19">
@@ -1113,20 +1135,22 @@
       </c>
       <c r="E19" s="10">
         <f>D19/C19</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="F19" s="8" t="n">
         <v>50</v>
       </c>
       <c r="G19" s="11">
         <f>C19-D19</f>
-        <v/>
+        <v>5.1</v>
       </c>
       <c r="H19" s="11">
         <f>G19*F19</f>
-        <v/>
-      </c>
-    </row>
+        <v>254.99999999999997</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
@@ -1140,6 +1164,15 @@
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>